--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486775_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486775_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6527</v>
+        <v>11.1396</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8729</v>
+        <v>4.8316</v>
       </c>
       <c r="F2" t="n">
-        <v>6.7799</v>
+        <v>6.308</v>
       </c>
       <c r="G2" t="n">
         <v>6.3371</v>
@@ -610,13 +610,13 @@
         <v>4.0546</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9822</v>
+        <v>0.4691</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1111</v>
+        <v>-0.1524</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0933</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>3.1749</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1801</v>
+        <v>5.3208</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6042</v>
+        <v>0.7698</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5758</v>
+        <v>4.551</v>
       </c>
       <c r="G3" t="n">
         <v>2.3603</v>
@@ -688,13 +688,13 @@
         <v>3.2823</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3971</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3867</v>
+        <v>-0.2212</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7839</v>
+        <v>0.7591</v>
       </c>
       <c r="V3" t="n">
         <v>0.1057</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0918</v>
+        <v>4.1222</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6823</v>
+        <v>1.7375</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4095</v>
+        <v>2.3847</v>
       </c>
       <c r="G4" t="n">
         <v>1.4884</v>
@@ -766,13 +766,13 @@
         <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3971</v>
+        <v>0.4275</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0272</v>
+        <v>0.0824</v>
       </c>
       <c r="U4" t="n">
-        <v>0.37</v>
+        <v>0.3451</v>
       </c>
       <c r="V4" t="n">
         <v>1.0478</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7787</v>
+        <v>3.3261</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.1726</v>
+        <v>-2.6003</v>
       </c>
       <c r="F5" t="n">
-        <v>5.9512</v>
+        <v>5.9264</v>
       </c>
       <c r="G5" t="n">
         <v>2.3228</v>
@@ -844,13 +844,13 @@
         <v>3.2823</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4301</v>
+        <v>0.1173</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9382</v>
+        <v>-0.3659</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5081</v>
+        <v>0.4833</v>
       </c>
       <c r="V5" t="n">
         <v>-0.4655</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>J. GARCIA CABRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.525</v>
+        <v>0.4171</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5349</v>
+        <v>-2.5239</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0599</v>
+        <v>2.941</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8532</v>
+        <v>1.0269</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0551</v>
+        <v>2.5166</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.798</v>
+        <v>-1.4897</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9826</v>
+        <v>-1.0479</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2954</v>
+        <v>1.1381</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6872</v>
+        <v>-2.1859</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1294</v>
+        <v>2.0747</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2403</v>
+        <v>1.3785</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1108</v>
+        <v>0.6962</v>
       </c>
       <c r="P6" t="n">
-        <v>2.51</v>
+        <v>1.3515</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4754</v>
+        <v>2.3169</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2757</v>
+        <v>-1.0619</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4131</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1374</v>
+        <v>-0.5512</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4076</v>
+        <v>-0.8995</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4076</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GARCIA CABRERA</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2156</v>
+        <v>0.2149</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4274</v>
+        <v>-3.0933</v>
       </c>
       <c r="F7" t="n">
-        <v>2.643</v>
+        <v>3.3082</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0269</v>
+        <v>-0.8532</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5166</v>
+        <v>-0.0551</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4897</v>
+        <v>-0.798</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0479</v>
+        <v>-1.9826</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1381</v>
+        <v>-1.2954</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.1859</v>
+        <v>-0.6872</v>
       </c>
       <c r="M7" t="n">
-        <v>2.0747</v>
+        <v>1.1294</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3785</v>
+        <v>1.2403</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6962</v>
+        <v>-0.1108</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3515</v>
+        <v>2.51</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3169</v>
+        <v>3.4754</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2634</v>
+        <v>-0.0344</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4142</v>
+        <v>-0.1453</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8492</v>
+        <v>0.1109</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8995</v>
+        <v>-1.4076</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8995</v>
+        <v>-1.4076</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7281</v>
+        <v>-0.4413</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2478</v>
+        <v>-0.9858</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5196</v>
+        <v>0.5445</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3104</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2592</v>
+        <v>0.0276</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1932</v>
+        <v>0.0688</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.066</v>
+        <v>-0.0412</v>
       </c>
       <c r="V8" t="n">
         <v>1.2277</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2731</v>
+        <v>-1.2483</v>
       </c>
       <c r="E10" t="n">
         <v>-0.9999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2732</v>
+        <v>-0.2484</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6553</v>
@@ -1234,13 +1234,13 @@
         <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0386</v>
+        <v>-0.0138</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9005</v>
+        <v>-1.5103</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2409</v>
+        <v>-1.8755</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3404</v>
+        <v>0.3652</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1102</v>
@@ -1312,13 +1312,13 @@
         <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1765</v>
+        <v>0.2138</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1932</v>
+        <v>0.1723</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0167</v>
+        <v>0.0415</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.821</v>
+        <v>-4.7921</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8988</v>
+        <v>-4.7954</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0033</v>
       </c>
       <c r="G12" t="n">
         <v>-5.613</v>
@@ -1390,13 +1390,13 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6288</v>
+        <v>-0.5999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6347</v>
+        <v>-0.5312</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0059</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>1.2277</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.004099999999999</v>
+        <v>8.8316</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.4862</v>
+        <v>-14.6585</v>
       </c>
       <c r="F14" t="n">
         <v>23.4901</v>
@@ -1546,13 +1546,13 @@
         <v>22.204</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6895</v>
+        <v>0.1380999999999997</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.3486</v>
+        <v>-1.5207</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6593</v>
+        <v>1.6592</v>
       </c>
       <c r="V14" t="n">
         <v>1.555800000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.594</v>
+        <v>3.2534</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7725</v>
+        <v>0.2553</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8216</v>
+        <v>2.9981</v>
       </c>
       <c r="G15" t="n">
         <v>2.6032</v>
@@ -1624,13 +1624,13 @@
         <v>2.3169</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3751</v>
+        <v>0.0345</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1925</v>
+        <v>-0.3246</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1826</v>
+        <v>0.3591</v>
       </c>
       <c r="V15" t="n">
         <v>-1.122</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1357</v>
+        <v>1.7934</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.5216</v>
+        <v>-2.0045</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6574</v>
+        <v>3.7979</v>
       </c>
       <c r="G16" t="n">
         <v>1.9587</v>
@@ -1702,13 +1702,13 @@
         <v>2.51</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8162</v>
+        <v>-0.1585</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2968</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4807</v>
+        <v>0.6212</v>
       </c>
       <c r="V16" t="n">
         <v>2.8893</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6257</v>
+        <v>1.3648</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2063</v>
+        <v>0.2074</v>
       </c>
       <c r="F17" t="n">
-        <v>0.832</v>
+        <v>1.1575</v>
       </c>
       <c r="G17" t="n">
         <v>2.234</v>
@@ -1780,13 +1780,13 @@
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5737</v>
+        <v>0.1655</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8002</v>
+        <v>-0.3865</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2265</v>
+        <v>0.552</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2277</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1638</v>
+        <v>-0.259</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.3258</v>
+        <v>-4.1189</v>
       </c>
       <c r="F18" t="n">
-        <v>3.162</v>
+        <v>3.8599</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8476</v>
@@ -1858,13 +1858,13 @@
         <v>2.1239</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4911</v>
+        <v>0.4137</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5246</v>
+        <v>-0.3178</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0335</v>
+        <v>0.7315</v>
       </c>
       <c r="V18" t="n">
         <v>1.3334</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9398</v>
+        <v>-1.435</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7145</v>
+        <v>-1.1585</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7747000000000001</v>
+        <v>-0.2764</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4423</v>
+        <v>-1.0209</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.813</v>
+        <v>-0.1935</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3707</v>
+        <v>-0.8274</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.7652</v>
+        <v>-1.2962</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1571</v>
+        <v>0.0828</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6081</v>
+        <v>-1.379</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3228</v>
+        <v>0.2753</v>
       </c>
       <c r="N19" t="n">
-        <v>0.344</v>
+        <v>-0.2763</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9788</v>
+        <v>0.5516</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5446</v>
+        <v>0.3862</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2823</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4547</v>
+        <v>0.4274</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8197</v>
+        <v>0.1377</v>
       </c>
       <c r="U19" t="n">
-        <v>0.635</v>
+        <v>0.2898</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4076</v>
+        <v>-1.2277</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.9209</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>J. DEL CASTILLO LEON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0722</v>
+        <v>-1.517</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5722</v>
+        <v>-3.6471</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4999</v>
+        <v>2.1301</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0209</v>
+        <v>-2.1793</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1935</v>
+        <v>-3.0135</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8274</v>
+        <v>0.8341</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2962</v>
+        <v>-2.3921</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0828</v>
+        <v>-2.3921</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.379</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2753</v>
+        <v>0.2128</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2763</v>
+        <v>-0.6214</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5516</v>
+        <v>0.8341</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3862</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.0892</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2098</v>
+        <v>0.7516</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.276</v>
+        <v>-0.0073</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0663</v>
+        <v>0.7589</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2277</v>
+        <v>1.8415</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. DEL CASTILLO LEON</t>
+          <t>P. JIMÉNEZ VELÁZQUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0975</v>
+        <v>-2.3592</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.1642</v>
+        <v>-1.4349</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0667</v>
+        <v>-0.9244</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1793</v>
+        <v>-0.9729</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.0135</v>
+        <v>-0.3241</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8341</v>
+        <v>-0.6488</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3921</v>
+        <v>-1.3176</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.3921</v>
+        <v>-0.6688</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.6488</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2128</v>
+        <v>0.3447</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6214</v>
+        <v>0.3447</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8341</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9308</v>
+        <v>0.1931</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0892</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1711</v>
+        <v>-0.3517</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5244</v>
+        <v>-0.1173</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6955</v>
+        <v>-0.2344</v>
       </c>
       <c r="V21" t="n">
-        <v>1.8415</v>
+        <v>-1.2277</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. JIMÉNEZ VELÁZQUEZ</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6254</v>
+        <v>-3.2568</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5383</v>
+        <v>-4.059</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0871</v>
+        <v>0.8021</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9729</v>
+        <v>-1.4423</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3241</v>
+        <v>-1.813</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6488</v>
+        <v>0.3707</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3176</v>
+        <v>-2.7652</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6688</v>
+        <v>-2.1571</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6488</v>
+        <v>-0.6081</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3447</v>
+        <v>1.3228</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3447</v>
+        <v>0.344</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.9788</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1931</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.2823</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1931</v>
+        <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6179</v>
+        <v>1.1377</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2207</v>
+        <v>0.4752</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3971</v>
+        <v>0.6625</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2277</v>
+        <v>-1.4076</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2277</v>
+        <v>-2.9209</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4607</v>
+        <v>-3.52</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.2196</v>
+        <v>-7.5299</v>
       </c>
       <c r="F23" t="n">
-        <v>3.7589</v>
+        <v>4.0099</v>
       </c>
       <c r="G23" t="n">
         <v>0.2528</v>
@@ -2248,13 +2248,13 @@
         <v>2.7031</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3971</v>
+        <v>0.3378</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0284</v>
+        <v>-0.3386</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4255</v>
+        <v>0.6765</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4076</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.004000000000001</v>
+        <v>-5.9354</v>
       </c>
       <c r="E24" t="n">
-        <v>-23.49</v>
+        <v>-23.4901</v>
       </c>
       <c r="F24" t="n">
-        <v>15.4863</v>
+        <v>17.5547</v>
       </c>
       <c r="G24" t="n">
         <v>0.5857000000000013</v>
@@ -2326,13 +2326,13 @@
         <v>14.4809</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6892999999999998</v>
+        <v>2.758</v>
       </c>
       <c r="T24" t="n">
         <v>-1.6589</v>
       </c>
       <c r="U24" t="n">
-        <v>2.3485</v>
+        <v>4.4171</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5561</v>
